--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2106,6 +2106,20 @@
         <v>291</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B120" t="n">
+        <v>278</v>
+      </c>
+      <c r="C120" t="n">
+        <v>283</v>
+      </c>
+      <c r="D120" t="n">
+        <v>294</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2120,6 +2120,20 @@
         <v>294</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B121" t="n">
+        <v>279</v>
+      </c>
+      <c r="C121" t="n">
+        <v>284</v>
+      </c>
+      <c r="D121" t="n">
+        <v>295</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2134,6 +2134,20 @@
         <v>295</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B122" t="n">
+        <v>281</v>
+      </c>
+      <c r="C122" t="n">
+        <v>288</v>
+      </c>
+      <c r="D122" t="n">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,6 +2148,20 @@
         <v>300</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B123" t="n">
+        <v>283</v>
+      </c>
+      <c r="C123" t="n">
+        <v>289</v>
+      </c>
+      <c r="D123" t="n">
+        <v>303</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,6 +2162,20 @@
         <v>303</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B124" t="n">
+        <v>285</v>
+      </c>
+      <c r="C124" t="n">
+        <v>293</v>
+      </c>
+      <c r="D124" t="n">
+        <v>307</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2176,6 +2176,20 @@
         <v>307</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B125" t="n">
+        <v>287</v>
+      </c>
+      <c r="C125" t="n">
+        <v>295</v>
+      </c>
+      <c r="D125" t="n">
+        <v>308</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2190,6 +2190,20 @@
         <v>308</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B126" t="n">
+        <v>288</v>
+      </c>
+      <c r="C126" t="n">
+        <v>295</v>
+      </c>
+      <c r="D126" t="n">
+        <v>312</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2204,6 +2204,20 @@
         <v>312</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B127" t="n">
+        <v>291</v>
+      </c>
+      <c r="C127" t="n">
+        <v>300</v>
+      </c>
+      <c r="D127" t="n">
+        <v>315</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2218,6 +2218,20 @@
         <v>315</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B128" t="n">
+        <v>294</v>
+      </c>
+      <c r="C128" t="n">
+        <v>300</v>
+      </c>
+      <c r="D128" t="n">
+        <v>316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2232,6 +2232,20 @@
         <v>316</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B129" t="n">
+        <v>297</v>
+      </c>
+      <c r="C129" t="n">
+        <v>304</v>
+      </c>
+      <c r="D129" t="n">
+        <v>319</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2246,6 +2246,20 @@
         <v>319</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B130" t="n">
+        <v>298</v>
+      </c>
+      <c r="C130" t="n">
+        <v>307</v>
+      </c>
+      <c r="D130" t="n">
+        <v>321</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2260,6 +2260,20 @@
         <v>321</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B131" t="n">
+        <v>301</v>
+      </c>
+      <c r="C131" t="n">
+        <v>312</v>
+      </c>
+      <c r="D131" t="n">
+        <v>322</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2274,6 +2274,20 @@
         <v>322</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B132" t="n">
+        <v>305</v>
+      </c>
+      <c r="C132" t="n">
+        <v>313</v>
+      </c>
+      <c r="D132" t="n">
+        <v>324</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2288,6 +2288,20 @@
         <v>324</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="B133" t="n">
+        <v>307</v>
+      </c>
+      <c r="C133" t="n">
+        <v>316</v>
+      </c>
+      <c r="D133" t="n">
+        <v>325</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2302,6 +2302,20 @@
         <v>325</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B134" t="n">
+        <v>311</v>
+      </c>
+      <c r="C134" t="n">
+        <v>319</v>
+      </c>
+      <c r="D134" t="n">
+        <v>328</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2316,6 +2316,20 @@
         <v>328</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B135" t="n">
+        <v>313</v>
+      </c>
+      <c r="C135" t="n">
+        <v>321</v>
+      </c>
+      <c r="D135" t="n">
+        <v>329</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2330,6 +2330,20 @@
         <v>329</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B136" t="n">
+        <v>316</v>
+      </c>
+      <c r="C136" t="n">
+        <v>324</v>
+      </c>
+      <c r="D136" t="n">
+        <v>334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2344,6 +2344,20 @@
         <v>334</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B137" t="n">
+        <v>319</v>
+      </c>
+      <c r="C137" t="n">
+        <v>325</v>
+      </c>
+      <c r="D137" t="n">
+        <v>336</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2358,6 +2358,20 @@
         <v>336</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B138" t="n">
+        <v>323</v>
+      </c>
+      <c r="C138" t="n">
+        <v>328</v>
+      </c>
+      <c r="D138" t="n">
+        <v>338</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2372,6 +2372,20 @@
         <v>338</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B139" t="n">
+        <v>325</v>
+      </c>
+      <c r="C139" t="n">
+        <v>330</v>
+      </c>
+      <c r="D139" t="n">
+        <v>342</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2386,6 +2386,20 @@
         <v>342</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B140" t="n">
+        <v>327</v>
+      </c>
+      <c r="C140" t="n">
+        <v>333</v>
+      </c>
+      <c r="D140" t="n">
+        <v>344</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2400,6 +2400,20 @@
         <v>344</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B141" t="n">
+        <v>330</v>
+      </c>
+      <c r="C141" t="n">
+        <v>334</v>
+      </c>
+      <c r="D141" t="n">
+        <v>347</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,6 +2414,20 @@
         <v>347</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B142" t="n">
+        <v>332</v>
+      </c>
+      <c r="C142" t="n">
+        <v>338</v>
+      </c>
+      <c r="D142" t="n">
+        <v>349</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,6 +2428,20 @@
         <v>349</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B143" t="n">
+        <v>334</v>
+      </c>
+      <c r="C143" t="n">
+        <v>341</v>
+      </c>
+      <c r="D143" t="n">
+        <v>352</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2442,6 +2442,20 @@
         <v>352</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B144" t="n">
+        <v>335</v>
+      </c>
+      <c r="C144" t="n">
+        <v>346</v>
+      </c>
+      <c r="D144" t="n">
+        <v>355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +2456,20 @@
         <v>355</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B145" t="n">
+        <v>335</v>
+      </c>
+      <c r="C145" t="n">
+        <v>348</v>
+      </c>
+      <c r="D145" t="n">
+        <v>361</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2470,6 +2470,20 @@
         <v>361</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B146" t="n">
+        <v>338</v>
+      </c>
+      <c r="C146" t="n">
+        <v>349</v>
+      </c>
+      <c r="D146" t="n">
+        <v>363</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2484,20 @@
         <v>363</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B147" t="n">
+        <v>339</v>
+      </c>
+      <c r="C147" t="n">
+        <v>352</v>
+      </c>
+      <c r="D147" t="n">
+        <v>369</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2498,6 +2498,20 @@
         <v>369</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="B148" t="n">
+        <v>343</v>
+      </c>
+      <c r="C148" t="n">
+        <v>353</v>
+      </c>
+      <c r="D148" t="n">
+        <v>369</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2512,6 +2512,20 @@
         <v>369</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B149" t="n">
+        <v>345</v>
+      </c>
+      <c r="C149" t="n">
+        <v>359</v>
+      </c>
+      <c r="D149" t="n">
+        <v>371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,6 +2526,20 @@
         <v>371</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B150" t="n">
+        <v>347</v>
+      </c>
+      <c r="C150" t="n">
+        <v>359</v>
+      </c>
+      <c r="D150" t="n">
+        <v>373</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2540,6 +2540,20 @@
         <v>373</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B151" t="n">
+        <v>352</v>
+      </c>
+      <c r="C151" t="n">
+        <v>363</v>
+      </c>
+      <c r="D151" t="n">
+        <v>376</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2554,6 +2554,20 @@
         <v>376</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B152" t="n">
+        <v>352</v>
+      </c>
+      <c r="C152" t="n">
+        <v>364</v>
+      </c>
+      <c r="D152" t="n">
+        <v>378</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D152"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,6 +2568,20 @@
         <v>378</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B153" t="n">
+        <v>357</v>
+      </c>
+      <c r="C153" t="n">
+        <v>365</v>
+      </c>
+      <c r="D153" t="n">
+        <v>382</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2582,6 +2582,20 @@
         <v>382</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B154" t="n">
+        <v>358</v>
+      </c>
+      <c r="C154" t="n">
+        <v>368</v>
+      </c>
+      <c r="D154" t="n">
+        <v>384</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2596,6 +2596,20 @@
         <v>384</v>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B155" t="n">
+        <v>362</v>
+      </c>
+      <c r="C155" t="n">
+        <v>371</v>
+      </c>
+      <c r="D155" t="n">
+        <v>386</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2610,6 +2610,20 @@
         <v>386</v>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B156" t="n">
+        <v>364</v>
+      </c>
+      <c r="C156" t="n">
+        <v>375</v>
+      </c>
+      <c r="D156" t="n">
+        <v>388</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D156"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2624,6 +2624,20 @@
         <v>388</v>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B157" t="n">
+        <v>364</v>
+      </c>
+      <c r="C157" t="n">
+        <v>377</v>
+      </c>
+      <c r="D157" t="n">
+        <v>393</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2638,6 +2638,20 @@
         <v>393</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B158" t="n">
+        <v>368</v>
+      </c>
+      <c r="C158" t="n">
+        <v>380</v>
+      </c>
+      <c r="D158" t="n">
+        <v>395</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2652,6 +2652,20 @@
         <v>395</v>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B159" t="n">
+        <v>368</v>
+      </c>
+      <c r="C159" t="n">
+        <v>383</v>
+      </c>
+      <c r="D159" t="n">
+        <v>398</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2666,6 +2666,20 @@
         <v>398</v>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B160" t="n">
+        <v>371</v>
+      </c>
+      <c r="C160" t="n">
+        <v>385</v>
+      </c>
+      <c r="D160" t="n">
+        <v>402</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2680,6 +2680,20 @@
         <v>402</v>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B161" t="n">
+        <v>373</v>
+      </c>
+      <c r="C161" t="n">
+        <v>385</v>
+      </c>
+      <c r="D161" t="n">
+        <v>403</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2694,6 +2694,20 @@
         <v>403</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B162" t="n">
+        <v>378</v>
+      </c>
+      <c r="C162" t="n">
+        <v>387</v>
+      </c>
+      <c r="D162" t="n">
+        <v>407</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D162"/>
+  <dimension ref="A1:D163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2708,6 +2708,20 @@
         <v>407</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B163" t="n">
+        <v>380</v>
+      </c>
+      <c r="C163" t="n">
+        <v>389</v>
+      </c>
+      <c r="D163" t="n">
+        <v>408</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,6 +2722,20 @@
         <v>408</v>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B164" t="n">
+        <v>384</v>
+      </c>
+      <c r="C164" t="n">
+        <v>392</v>
+      </c>
+      <c r="D164" t="n">
+        <v>411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2736,6 +2736,20 @@
         <v>411</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B165" t="n">
+        <v>386</v>
+      </c>
+      <c r="C165" t="n">
+        <v>395</v>
+      </c>
+      <c r="D165" t="n">
+        <v>413</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:D166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2750,6 +2750,20 @@
         <v>413</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B166" t="n">
+        <v>387</v>
+      </c>
+      <c r="C166" t="n">
+        <v>397</v>
+      </c>
+      <c r="D166" t="n">
+        <v>416</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D166"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2764,6 +2764,20 @@
         <v>416</v>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B167" t="n">
+        <v>392</v>
+      </c>
+      <c r="C167" t="n">
+        <v>403</v>
+      </c>
+      <c r="D167" t="n">
+        <v>420</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2778,6 +2778,20 @@
         <v>420</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B168" t="n">
+        <v>398</v>
+      </c>
+      <c r="C168" t="n">
+        <v>405</v>
+      </c>
+      <c r="D168" t="n">
+        <v>427</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
